--- a/reconciler/reconciler-demo.xlsx
+++ b/reconciler/reconciler-demo.xlsx
@@ -971,7 +971,7 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>Built by Automated Workflow LLC  ·  automatedworkflowllc.com  ·  the Reconciler</t>
+          <t>Built by Automated Workflow  ·  automatedworkflowllc.com  ·  the Reconciler</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>Built by Automated Workflow LLC  ·  automatedworkflowllc.com  ·  the Reconciler</t>
+          <t>Built by Automated Workflow  ·  automatedworkflowllc.com  ·  the Reconciler</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>Built by Automated Workflow LLC  ·  automatedworkflowllc.com  ·  the Reconciler</t>
+          <t>Built by Automated Workflow  ·  automatedworkflowllc.com  ·  the Reconciler</t>
         </is>
       </c>
     </row>
